--- a/docs/Mapping_casi_uso/unioni_civili/UnCiv_998_2.xlsx
+++ b/docs/Mapping_casi_uso/unioni_civili/UnCiv_998_2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="77">
   <si>
     <t>Sezione</t>
   </si>
@@ -129,12 +129,6 @@
   </si>
   <si>
     <t>idAttoCartaceo</t>
-  </si>
-  <si>
-    <t>Atto secretato</t>
-  </si>
-  <si>
-    <t>flagsecretato</t>
   </si>
   <si>
     <t>Ente dichiarante</t>
@@ -307,7 +301,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -643,19 +637,19 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
@@ -666,16 +660,16 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -689,16 +683,16 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -712,7 +706,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
@@ -721,7 +715,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -735,7 +729,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
@@ -744,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -758,7 +752,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
@@ -767,7 +761,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -781,16 +775,16 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>54</v>
@@ -804,19 +798,19 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
@@ -827,16 +821,16 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>60</v>
@@ -850,7 +844,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>61</v>
@@ -859,7 +853,7 @@
         <v>13</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>62</v>
@@ -873,7 +867,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>63</v>
@@ -882,7 +876,7 @@
         <v>13</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -896,7 +890,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
@@ -905,7 +899,7 @@
         <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -919,7 +913,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
@@ -928,10 +922,10 @@
         <v>13</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
@@ -942,19 +936,19 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>10</v>
@@ -965,7 +959,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>70</v>
@@ -974,10 +968,10 @@
         <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>10</v>
@@ -988,19 +982,19 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>10</v>
@@ -1011,7 +1005,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>73</v>
@@ -1020,7 +1014,7 @@
         <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>74</v>
@@ -1034,13 +1028,13 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>17</v>
@@ -1052,29 +1046,6 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="2" t="s">
         <v>19</v>
       </c>
     </row>
